--- a/evidence-room/03_AP_AGENT_OS_PRO/Spreadsheets/ER_AP_Exception_Tracker.xlsx
+++ b/evidence-room/03_AP_AGENT_OS_PRO/Spreadsheets/ER_AP_Exception_Tracker.xlsx
@@ -9,6 +9,8 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TAXONOMY" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OPEN_ITEMS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EXAMPLE_OPEN" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RULES" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1089,4 +1091,343 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Work object</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Supplier</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Age (days)</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Next action</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Autonomy</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>WO-10412</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>EX-MGR</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Northline Steel Co (fictional)</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>18420</v>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Plant Cleveland</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>Receiver packet</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>WO-10488</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>EX-PRC</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Helix Fasteners (fictional)</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>960</v>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Match desk</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Tolerance check</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>WO-10501</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>EX-PDUP</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Helix Fasteners (fictional)</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>960</v>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Controls</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Human clearance</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>L0</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>WO-10302</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>EX-APP</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Officepath (fictional)</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>2400</v>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>DOA owner</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Chase packet</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>WO-10211</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>EX-BNK</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Delta Castings (fictional)</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>44100</v>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Controller</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>02/12</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Hold — human only</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>L1 annotate</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>hold</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Closed list only. Free-text “other” is a design smell. EX-BNK and payment holds are human. Northline names are fictional.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>